--- a/Project 1 (DATA CLEANING).xlsx
+++ b/Project 1 (DATA CLEANING).xlsx
@@ -12910,13 +12910,13 @@
     <t>Data Formats</t>
   </si>
   <si>
-    <t>everything correct (Date, Time)</t>
-  </si>
-  <si>
     <t>Quantity*Unit Price</t>
   </si>
   <si>
     <t>equals to Total Price</t>
+  </si>
+  <si>
+    <t>everything correct (Date, Number formats)</t>
   </si>
 </sst>
 </file>
@@ -13003,16 +13003,6 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -13058,26 +13048,29 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -13108,6 +13101,13 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -13122,27 +13122,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:P1202" totalsRowCount="1" headerRowDxfId="21" dataDxfId="1" headerRowBorderDxfId="19" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:P1202" totalsRowCount="1" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17">
   <autoFilter ref="A1:P1201"/>
   <tableColumns count="16">
-    <tableColumn id="1" name="OrderID" dataDxfId="17"/>
-    <tableColumn id="2" name="Date" dataDxfId="16" totalsRowDxfId="18"/>
-    <tableColumn id="3" name="CustomerID" dataDxfId="15"/>
-    <tableColumn id="4" name="Product" dataDxfId="14"/>
-    <tableColumn id="5" name="Quantity" dataDxfId="13"/>
-    <tableColumn id="6" name="UnitPrice" dataDxfId="12"/>
-    <tableColumn id="7" name="ShippingAddress" dataDxfId="11"/>
-    <tableColumn id="8" name="PaymentMethod" dataDxfId="10"/>
-    <tableColumn id="9" name="OrderStatus" dataDxfId="9"/>
-    <tableColumn id="10" name="TrackingNumber" dataDxfId="8"/>
-    <tableColumn id="11" name="ItemsInCart" dataDxfId="7"/>
-    <tableColumn id="12" name="CouponCode" dataDxfId="6"/>
-    <tableColumn id="13" name="ReferralSource" dataDxfId="5"/>
-    <tableColumn id="14" name="TotalPrice" dataDxfId="4"/>
-    <tableColumn id="18" name="Check Total Price" dataDxfId="3">
+    <tableColumn id="1" name="OrderID" dataDxfId="16"/>
+    <tableColumn id="2" name="Date" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="3" name="CustomerID" dataDxfId="13"/>
+    <tableColumn id="4" name="Product" dataDxfId="12"/>
+    <tableColumn id="5" name="Quantity" dataDxfId="11"/>
+    <tableColumn id="6" name="UnitPrice" dataDxfId="10"/>
+    <tableColumn id="7" name="ShippingAddress" dataDxfId="9"/>
+    <tableColumn id="8" name="PaymentMethod" dataDxfId="8"/>
+    <tableColumn id="9" name="OrderStatus" dataDxfId="7"/>
+    <tableColumn id="10" name="TrackingNumber" dataDxfId="6"/>
+    <tableColumn id="11" name="ItemsInCart" dataDxfId="5"/>
+    <tableColumn id="12" name="CouponCode" dataDxfId="4"/>
+    <tableColumn id="13" name="ReferralSource" dataDxfId="3"/>
+    <tableColumn id="14" name="TotalPrice" dataDxfId="2"/>
+    <tableColumn id="18" name="Check Total Price" dataDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[UnitPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Final check Total Price" dataDxfId="2">
+    <tableColumn id="19" name="Final check Total Price" dataDxfId="0">
       <calculatedColumnFormula>ROUND(Table1[[#This Row],[TotalPrice]],2)=ROUND(Table1[[#This Row],[Check Total Price]],2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13489,15 +13489,15 @@
         <v>4294</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4295</v>
+        <v>4297</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>4295</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>4296</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>4297</v>
       </c>
     </row>
   </sheetData>
@@ -75988,7 +75988,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:N1201">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="21" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
